--- a/data-raw/su_translations.xlsx
+++ b/data-raw/su_translations.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6496" uniqueCount="4905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6518" uniqueCount="4920">
   <si>
     <t xml:space="preserve">@ note: comments are marked with @ and sections are marked with @@</t>
   </si>
@@ -2795,8 +2795,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">となる。
-</t>
+      <t xml:space="preserve">となる。</t>
     </r>
   </si>
   <si>
@@ -3047,8 +3046,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">となる
-</t>
+      <t xml:space="preserve">となる</t>
     </r>
   </si>
   <si>
@@ -22891,6 +22889,51 @@
   </si>
   <si>
     <t xml:space="preserve">reception side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">players without assigned role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他選手</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jogadores sem posições</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jugadores sin roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joueurs sans positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giocatori senza ruolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shortace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">số ace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all attackers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すべてのアタッカー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">todos os atacantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">todos los atacantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tous les attaquants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tutti gli attaccanti</t>
   </si>
 </sst>
 </file>
@@ -23054,7 +23097,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -23116,6 +23159,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -23302,7 +23349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMK1427"/>
+  <dimension ref="A1:AMK1429"/>
   <sheetFormatPr defaultColWidth="63.36328125" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="63.29"/>
@@ -26222,7 +26269,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="143.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="129.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>705</v>
       </c>
@@ -26248,7 +26295,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="143.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="129.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>712</v>
       </c>
@@ -47029,25 +47076,89 @@
       <c r="C1002" s="2"/>
     </row>
     <row r="1003" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1003" s="2"/>
+      <c r="A1003" s="1" t="s">
+        <v>4905</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>4905</v>
+      </c>
+      <c r="C1003" s="5" t="s">
+        <v>4906</v>
+      </c>
+      <c r="E1003" s="1" t="s">
+        <v>4907</v>
+      </c>
+      <c r="F1003" s="1" t="s">
+        <v>4908</v>
+      </c>
+      <c r="G1003" s="1" t="s">
+        <v>4909</v>
+      </c>
+      <c r="H1003" s="1" t="s">
+        <v>4910</v>
+      </c>
     </row>
     <row r="1004" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1004" s="2"/>
-    </row>
-    <row r="1005" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1005" s="2"/>
-    </row>
-    <row r="1006" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1006" s="2"/>
-    </row>
-    <row r="1007" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1007" s="2"/>
-    </row>
-    <row r="1008" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1008" s="2"/>
-    </row>
-    <row r="1009" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1009" s="2"/>
+      <c r="A1004" s="1" t="s">
+        <v>4911</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C1004" s="16" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D1004" s="15" t="s">
+        <v>4912</v>
+      </c>
+      <c r="E1004" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F1004" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G1004" s="1" t="s">
+        <v>4913</v>
+      </c>
+      <c r="H1004" s="1" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="1005" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1005" s="15" t="s">
+        <v>4914</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>4914</v>
+      </c>
+      <c r="C1005" s="5" t="s">
+        <v>4915</v>
+      </c>
+      <c r="E1005" s="1" t="s">
+        <v>4916</v>
+      </c>
+      <c r="F1005" s="1" t="s">
+        <v>4917</v>
+      </c>
+      <c r="G1005" s="1" t="s">
+        <v>4918</v>
+      </c>
+      <c r="H1005" s="1" t="s">
+        <v>4919</v>
+      </c>
+    </row>
+    <row r="1006" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1006" s="5"/>
+    </row>
+    <row r="1007" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1007" s="5"/>
+    </row>
+    <row r="1008" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1008" s="5"/>
+      <c r="H1008" s="7"/>
+    </row>
+    <row r="1009" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1009" s="5"/>
     </row>
     <row r="1010" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1010" s="2"/>
@@ -48302,6 +48413,12 @@
     </row>
     <row r="1427" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1427" s="2"/>
+    </row>
+    <row r="1428" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C1428" s="2"/>
+    </row>
+    <row r="1429" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C1429" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
